--- a/all_books.xlsx
+++ b/all_books.xlsx
@@ -14,51 +14,207 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Client Name</t>
-  </si>
-  <si>
-    <t>CLient Email</t>
-  </si>
-  <si>
-    <t>CLient NationalID</t>
-  </si>
-  <si>
-    <t>mahmoud</t>
-  </si>
-  <si>
-    <t>mahmoud@gmail.com</t>
-  </si>
-  <si>
-    <t>2123213124</t>
-  </si>
-  <si>
-    <t>ahmed</t>
-  </si>
-  <si>
-    <t>ahmed@gmail.com</t>
-  </si>
-  <si>
-    <t>21232674676</t>
-  </si>
-  <si>
-    <t>jack</t>
-  </si>
-  <si>
-    <t>jack22@gmail.com</t>
-  </si>
-  <si>
-    <t>123142423</t>
-  </si>
-  <si>
-    <t>john33</t>
-  </si>
-  <si>
-    <t>john33@gmail.com</t>
-  </si>
-  <si>
-    <t>4534636346</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+  <si>
+    <t>Book Code</t>
+  </si>
+  <si>
+    <t>Book Name</t>
+  </si>
+  <si>
+    <t>Book Description</t>
+  </si>
+  <si>
+    <t>Book Category</t>
+  </si>
+  <si>
+    <t>Book Author</t>
+  </si>
+  <si>
+    <t>Book publisher</t>
+  </si>
+  <si>
+    <t>Book Price</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Python Programming</t>
+  </si>
+  <si>
+    <t>An introduction to Python</t>
+  </si>
+  <si>
+    <t>Drama</t>
+  </si>
+  <si>
+    <t>Jane Doe</t>
+  </si>
+  <si>
+    <t>Penguin Books</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Java Basics</t>
+  </si>
+  <si>
+    <t>A beginner guide to Java</t>
+  </si>
+  <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>The Great Adventure</t>
+  </si>
+  <si>
+    <t>A thrilling adventure story</t>
+  </si>
+  <si>
+    <t>Fiction</t>
+  </si>
+  <si>
+    <t>Alice Johnson</t>
+  </si>
+  <si>
+    <t>Random House</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Deep Learning Explained</t>
+  </si>
+  <si>
+    <t>A comprehensive guide to deep learning</t>
+  </si>
+  <si>
+    <t>Gaming</t>
+  </si>
+  <si>
+    <t>OReilly Media</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>Cooking with Love</t>
+  </si>
+  <si>
+    <t>Recipes and tips for home cooks</t>
+  </si>
+  <si>
+    <t>Cooking</t>
+  </si>
+  <si>
+    <t>Good Food Press</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>Sports and Fitness</t>
+  </si>
+  <si>
+    <t>A guide to staying fit</t>
+  </si>
+  <si>
+    <t>Sport</t>
+  </si>
+  <si>
+    <t>Sports House</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>Drama Unfolded</t>
+  </si>
+  <si>
+    <t>Stories from everyday lives</t>
+  </si>
+  <si>
+    <t>Chris Brown</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>Gaming Tricks</t>
+  </si>
+  <si>
+    <t>Top tricks for gaming</t>
+  </si>
+  <si>
+    <t>Michael Fox</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Space Exploration</t>
+  </si>
+  <si>
+    <t>Facts and fantasies of outer space</t>
+  </si>
+  <si>
+    <t>Sarah Connor</t>
+  </si>
+  <si>
+    <t>SciTech Press</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>Learn SQL</t>
+  </si>
+  <si>
+    <t>A guide to learn SQL effectively</t>
+  </si>
+  <si>
+    <t>SQL Academy</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>Lord of the Rings</t>
   </si>
 </sst>
 </file>
@@ -390,10 +546,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -403,49 +559,267 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
